--- a/Evaluation/pool2025_26/poolResults.xlsx
+++ b/Evaluation/pool2025_26/poolResults.xlsx
@@ -1,34 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javier.alonsov\Documents\Curso25_26\Investigacion\UB\Innovacio2025\results\pool2025_26\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javit\Documents\UB_aulaSDR\Evaluation\pool2025_26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09F6E82-CB27-49E5-BB0B-8EBA2332EDB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D28ABD10-3BF2-4D37-BBBB-3A3A3B56B50D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$A$25</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$A$26</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">Sheet1!$B$27:$T$27</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">Sheet1!$B$27:$T$27</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">Sheet1!$B$18:$T$18</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$A$27</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$B$1:$W$24</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$B$25:$W$25</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$B$26:$W$26</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Sheet1!$B$27:$W$27</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Sheet1!$B$12:$T$12</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Sheet1!$B$6:$T$6</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">Sheet1!$B$23:$T$23</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$B$18:$T$18</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$B$23:$T$23</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$B$12:$T$12</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$B$6:$T$6</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$B$27:$T$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,9 +35,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -190,9 +179,6 @@
 con Teoría de Coms.</t>
   </si>
   <si>
-    <t>Evaluación Golbal</t>
-  </si>
-  <si>
     <t>Satisfecho</t>
   </si>
   <si>
@@ -203,6 +189,9 @@
   </si>
   <si>
     <t>Resultados Sección</t>
+  </si>
+  <si>
+    <t>Evaluación Global</t>
   </si>
 </sst>
 </file>
@@ -306,7 +295,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f dir="row">_xlchart.v1.8</cx:f>
+        <cx:f dir="row">_xlchart.v1.3</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -367,7 +356,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f dir="row">_xlchart.v1.7</cx:f>
+        <cx:f dir="row">_xlchart.v1.2</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -428,7 +417,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f dir="row">_xlchart.v1.12</cx:f>
+        <cx:f dir="row">_xlchart.v1.0</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -489,7 +478,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f dir="row">_xlchart.v1.9</cx:f>
+        <cx:f dir="row">_xlchart.v1.1</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -550,7 +539,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f dir="row">_xlchart.v1.10</cx:f>
+        <cx:f dir="row">_xlchart.v1.4</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -3395,8 +3384,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="15357434" y="0"/>
-              <a:ext cx="4576142" cy="1911153"/>
+              <a:off x="15286204" y="0"/>
+              <a:ext cx="4552950" cy="1911153"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -3416,8 +3405,8 @@
             <a:p>
               <a:r>
                 <a:rPr lang="ca-ES" sz="1100"/>
-                <a:t>Aquest gràfic no està disponible en la vostra versió del Excel.
- Si editeu aquesta forma o deseu aquesta llibreta en un format de fitxer diferent, el gràfic quedarà malmès permanentment.</a:t>
+                <a:t>Este gráfico no está disponible en su versión de Excel.
+Si edita esta forma o guarda el libro en un formato de archivo diferente, el gráfico no se podrá utilizar.</a:t>
               </a:r>
             </a:p>
           </xdr:txBody>
@@ -3473,8 +3462,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="15158499" y="1929550"/>
-              <a:ext cx="4541441" cy="1858038"/>
+              <a:off x="15254870" y="1929550"/>
+              <a:ext cx="4572817" cy="1858038"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -3494,8 +3483,8 @@
             <a:p>
               <a:r>
                 <a:rPr lang="ca-ES" sz="1100"/>
-                <a:t>Aquest gràfic no està disponible en la vostra versió del Excel.
- Si editeu aquesta forma o deseu aquesta llibreta en un format de fitxer diferent, el gràfic quedarà malmès permanentment.</a:t>
+                <a:t>Este gráfico no está disponible en su versión de Excel.
+Si edita esta forma o guarda el libro en un formato de archivo diferente, el gráfico no se podrá utilizar.</a:t>
               </a:r>
             </a:p>
           </xdr:txBody>
@@ -3551,8 +3540,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="15328846" y="3767097"/>
-              <a:ext cx="4592011" cy="2138403"/>
+              <a:off x="15263532" y="3767097"/>
+              <a:ext cx="4572961" cy="2138403"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -3572,8 +3561,8 @@
             <a:p>
               <a:r>
                 <a:rPr lang="ca-ES" sz="1100"/>
-                <a:t>Aquest gràfic no està disponible en la vostra versió del Excel.
- Si editeu aquesta forma o deseu aquesta llibreta en un format de fitxer diferent, el gràfic quedarà malmès permanentment.</a:t>
+                <a:t>Este gráfico no está disponible en su versión de Excel.
+Si edita esta forma o guarda el libro en un formato de archivo diferente, el gráfico no se podrá utilizar.</a:t>
               </a:r>
             </a:p>
           </xdr:txBody>
@@ -3629,8 +3618,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="15280820" y="5921828"/>
-              <a:ext cx="4626429" cy="1766208"/>
+              <a:off x="15215506" y="5921828"/>
+              <a:ext cx="4607379" cy="1575708"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -3650,8 +3639,8 @@
             <a:p>
               <a:r>
                 <a:rPr lang="ca-ES" sz="1100"/>
-                <a:t>Aquest gràfic no està disponible en la vostra versió del Excel.
- Si editeu aquesta forma o deseu aquesta llibreta en un format de fitxer diferent, el gràfic quedarà malmès permanentment.</a:t>
+                <a:t>Este gráfico no está disponible en su versión de Excel.
+Si edita esta forma o guarda el libro en un formato de archivo diferente, el gráfico no se podrá utilizar.</a:t>
               </a:r>
             </a:p>
           </xdr:txBody>
@@ -3707,8 +3696,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="15321643" y="7663542"/>
-              <a:ext cx="4572000" cy="2743200"/>
+              <a:off x="15256329" y="7473042"/>
+              <a:ext cx="4552950" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -3728,8 +3717,8 @@
             <a:p>
               <a:r>
                 <a:rPr lang="ca-ES" sz="1100"/>
-                <a:t>Aquest gràfic no està disponible en la vostra versió del Excel.
- Si editeu aquesta forma o deseu aquesta llibreta en un format de fitxer diferent, el gràfic quedarà malmès permanentment.</a:t>
+                <a:t>Este gráfico no está disponible en su versión de Excel.
+Si edita esta forma o guarda el libro en un formato de archivo diferente, el gráfico no se podrá utilizar.</a:t>
               </a:r>
             </a:p>
           </xdr:txBody>
@@ -4005,7 +3994,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.85546875" customWidth="1"/>
   </cols>
@@ -4379,7 +4368,7 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6">
         <f>MEDIAN(B2:B5)</f>
@@ -4827,7 +4816,7 @@
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B12">
         <f>MEDIAN(B8:B11)</f>
@@ -5275,7 +5264,7 @@
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B18">
         <f>MEDIAN(B14:B17)</f>
@@ -5425,7 +5414,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>38</v>
       </c>
@@ -5649,7 +5638,7 @@
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B23">
         <f>MEDIAN(B20:B22)</f>
@@ -5730,7 +5719,7 @@
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>5</v>
@@ -5801,7 +5790,7 @@
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B25">
         <v>2</v>
@@ -5875,7 +5864,7 @@
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B26">
         <v>3</v>
@@ -5949,7 +5938,7 @@
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B27">
         <f>MEDIAN(B25:B26)</f>
